--- a/output/model_performance_table.xlsx
+++ b/output/model_performance_table.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.931</v>
+        <v>0.9310009718172982</v>
       </c>
       <c r="C2" t="n">
-        <v>0.724</v>
+        <v>0.7244897959183674</v>
       </c>
       <c r="D2" t="n">
-        <v>0.846</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.878</v>
+        <v>0.8775510204081632</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.912</v>
+        <v>0.9122934888241011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.724</v>
+        <v>0.7244897959183674</v>
       </c>
       <c r="D3" t="n">
-        <v>0.802</v>
+        <v>0.8021978021978022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.796</v>
+        <v>0.7959183673469388</v>
       </c>
     </row>
   </sheetData>
